--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132784615</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132784615</v>
+        <v>132784602</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592250</v>
+        <v>592271</v>
       </c>
       <c r="R2" t="n">
-        <v>6710834</v>
+        <v>6710810</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -788,6 +788,698 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132784615</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>592250</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6710834</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132784665</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>592231</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6710876</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132784707</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592172</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6710922</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133238219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knärot1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592231</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6710803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132784402</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knärot1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592202</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6710809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132785250</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710810</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132784602</v>
+        <v>133098853</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Döda granar, Gstr</t>
+          <t>Knärot1, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592271</v>
+        <v>592231</v>
       </c>
       <c r="R2" t="n">
-        <v>6710810</v>
+        <v>6710803</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132784615</v>
+        <v>132784602</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592250</v>
+        <v>592271</v>
       </c>
       <c r="R3" t="n">
-        <v>6710834</v>
+        <v>6710810</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132784665</v>
+        <v>132784615</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592231</v>
+        <v>592250</v>
       </c>
       <c r="R4" t="n">
-        <v>6710876</v>
+        <v>6710834</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132784707</v>
+        <v>132784665</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592172</v>
+        <v>592231</v>
       </c>
       <c r="R5" t="n">
-        <v>6710922</v>
+        <v>6710876</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,27 +1139,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133238219</v>
+        <v>132784707</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,7 +1167,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1175,14 +1179,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knärot1, Gstr</t>
+          <t>Döda granar, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592231</v>
+        <v>592172</v>
       </c>
       <c r="R6" t="n">
-        <v>6710803</v>
+        <v>6710922</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,29 +1213,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1251,37 +1255,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132784402</v>
+        <v>133238219</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1290,67 +1295,62 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592202</v>
+        <v>592231</v>
       </c>
       <c r="R7" t="n">
-        <v>6710809</v>
+        <v>6710803</v>
       </c>
       <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
         <v>1</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sandviken</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Årsunda</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132785250</v>
+        <v>132784402</v>
       </c>
       <c r="B8" t="n">
         <v>99195</v>
@@ -1397,27 +1397,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Döda granar, Gstr</t>
+          <t>Knärot1, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592271</v>
+        <v>592202</v>
       </c>
       <c r="R8" t="n">
-        <v>6710810</v>
+        <v>6710809</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,6 +1462,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1480,6 +1480,122 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132785250</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710810</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784602</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784615</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133238219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784402</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,8 +1636,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>133098853</v>
       </c>
       <c r="B2" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>133098853</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
